--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondLendTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondLendTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspaces_idea\branch_yitihua_version_bs1.9_20190625\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>券面总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交易日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,6 +76,10 @@
   </si>
   <si>
     <t>币种</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>券面总额/万元</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,28 +485,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondLendTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondLendTrade001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workSpaceGZNEW\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20385" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20390" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,17 +36,6 @@
     <t>委托代码</t>
   </si>
   <si>
-    <t>交易方向</t>
-  </si>
-  <si>
-    <t>标的债券代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标的债券名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交易场所</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,6 +69,18 @@
   </si>
   <si>
     <t>券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标的债券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>借贷方向</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -447,16 +448,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="15.625" customWidth="1"/>
-    <col min="9" max="9" width="15.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.625" style="2" customWidth="1"/>
-    <col min="11" max="12" width="15.625" customWidth="1"/>
+    <col min="1" max="8" width="15.6328125" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6328125" style="2" customWidth="1"/>
+    <col min="11" max="12" width="15.6328125" customWidth="1"/>
     <col min="13" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,40 +474,40 @@
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
